--- a/docs/demo-import/题库导入_物理_演示.xlsx
+++ b/docs/demo-import/题库导入_物理_演示.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="题目检查" sheetId="1" r:id="Rc3b33368a9ed4d55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="Rcc6893b401384569"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="题目检查" sheetId="1" r:id="R75b9b72a1afb4a2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="Rb889c94395bd4443"/>
   </x:sheets>
 </x:workbook>
 </file>
